--- a/challenge-2/unstructured_files/Procurement Thresholds 2024-25.xlsx
+++ b/challenge-2/unstructured_files/Procurement Thresholds 2024-25.xlsx
@@ -779,7 +779,7 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>Note 2: FTS thresholds are updated every two years by the Cabinet Office</t>
+          <t>Note 2: FTS thresholds are updated every two years by the [Central Government Body]</t>
         </is>
       </c>
     </row>
